--- a/education_forms/041_open_source_learning_tool_request_form--education_forms.xlsx
+++ b/education_forms/041_open_source_learning_tool_request_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1171,8 +1171,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'category',_'value':_'category_a'}</t>
+          <t>category_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Category', 'value': 'Category A'}</t>
+          <t>Category A</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'category_b',_'value':_'category_b'}</t>
+          <t>category_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Category B', 'value': 'Category B'}</t>
+          <t>Category B</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'category_c',_'value':_'category_c'}</t>
+          <t>category_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Category C', 'value': 'Category C'}</t>
+          <t>Category C</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'submit_form',_'value':_'submit_form'}</t>
+          <t>submit_form</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Submit Form', 'value': 'Submit Form'}</t>
+          <t>Submit Form</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'cancel',_'value':_'cancel'}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Cancel', 'value': 'Cancel'}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'save_as_draft',_'value':_'save_as_draft'}</t>
+          <t>save_as_draft</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Save as Draft', 'value': 'Save as Draft'}</t>
+          <t>Save as Draft</t>
         </is>
       </c>
     </row>
